--- a/BVSimulationFiles/92.xlsx
+++ b/BVSimulationFiles/92.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0004725274725274725</v>
+        <v>0.000945054945054945</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004903639283782444</v>
+        <v>0.0009807278567564887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005080613700043555</v>
+        <v>0.001016122740008711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005256205839973419</v>
+        <v>0.001051241167994684</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000543042353023373</v>
+        <v>0.001086084706046746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005603274558415614</v>
+        <v>0.001120654911683123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000577476667322187</v>
+        <v>0.001154953334644374</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005944907584648429</v>
+        <v>0.001188981516929686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006113704964164982</v>
+        <v>0.001222740992832996</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006281166444894807</v>
+        <v>0.001256233288978961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006447299621793793</v>
+        <v>0.001289459924358759</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006612112051828657</v>
+        <v>0.001322422410365731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006775611254154375</v>
+        <v>0.001355122250830875</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0006937804710290807</v>
+        <v>0.001387560942058161</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007098699864298533</v>
+        <v>0.001419739972859707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007258304122953915</v>
+        <v>0.001451660824590783</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007416624855923356</v>
+        <v>0.001483324971184671</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007573669395936799</v>
+        <v>0.00151473387918736</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007729445038960422</v>
+        <v>0.001545889007792084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007883959044368599</v>
+        <v>0.00157679180887372</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0004725274725274725</v>
+        <v>0.000945054945054945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004903639283782444</v>
+        <v>0.0009807278567564887</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005080613700043555</v>
+        <v>0.001016122740008711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005256205839973419</v>
+        <v>0.001051241167994684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000543042353023373</v>
+        <v>0.001086084706046746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005603274558415614</v>
+        <v>0.001120654911683123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000577476667322187</v>
+        <v>0.001154953334644374</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005944907584648429</v>
+        <v>0.001188981516929686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006113704964164982</v>
+        <v>0.001222740992832996</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006281166444894807</v>
+        <v>0.001256233288978961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006447299621793793</v>
+        <v>0.001289459924358759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006612112051828657</v>
+        <v>0.001322422410365731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006775611254154375</v>
+        <v>0.001355122250830875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006937804710290807</v>
+        <v>0.001387560942058161</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007098699864298533</v>
+        <v>0.001419739972859707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007258304122953915</v>
+        <v>0.001451660824590783</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007416624855923356</v>
+        <v>0.001483324971184671</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007573669395936799</v>
+        <v>0.00151473387918736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007729445038960422</v>
+        <v>0.001545889007792084</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007883959044368599</v>
+        <v>0.00157679180887372</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/92.xlsx
+++ b/BVSimulationFiles/92.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000945054945054945</v>
+        <v>0.009450549450549449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009807278567564887</v>
+        <v>0.009807278567564887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001016122740008711</v>
+        <v>0.01016122740008711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001051241167994684</v>
+        <v>0.01051241167994684</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001086084706046746</v>
+        <v>0.01086084706046746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001120654911683123</v>
+        <v>0.01120654911683123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001154953334644374</v>
+        <v>0.01154953334644374</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001188981516929686</v>
+        <v>0.01188981516929686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001222740992832996</v>
+        <v>0.01222740992832996</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001256233288978961</v>
+        <v>0.01256233288978961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001289459924358759</v>
+        <v>0.01289459924358759</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001322422410365731</v>
+        <v>0.01322422410365731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001355122250830875</v>
+        <v>0.01355122250830875</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001387560942058161</v>
+        <v>0.01387560942058161</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001419739972859707</v>
+        <v>0.01419739972859707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001451660824590783</v>
+        <v>0.01451660824590783</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001483324971184671</v>
+        <v>0.01483324971184671</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00151473387918736</v>
+        <v>0.0151473387918736</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001545889007792084</v>
+        <v>0.01545889007792084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00157679180887372</v>
+        <v>0.0157679180887372</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000945054945054945</v>
+        <v>0.009450549450549449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009807278567564887</v>
+        <v>0.009807278567564887</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001016122740008711</v>
+        <v>0.01016122740008711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001051241167994684</v>
+        <v>0.01051241167994684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001086084706046746</v>
+        <v>0.01086084706046746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001120654911683123</v>
+        <v>0.01120654911683123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001154953334644374</v>
+        <v>0.01154953334644374</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001188981516929686</v>
+        <v>0.01188981516929686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001222740992832996</v>
+        <v>0.01222740992832996</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001256233288978961</v>
+        <v>0.01256233288978961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001289459924358759</v>
+        <v>0.01289459924358759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001322422410365731</v>
+        <v>0.01322422410365731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001355122250830875</v>
+        <v>0.01355122250830875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001387560942058161</v>
+        <v>0.01387560942058161</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001419739972859707</v>
+        <v>0.01419739972859707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001451660824590783</v>
+        <v>0.01451660824590783</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001483324971184671</v>
+        <v>0.01483324971184671</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00151473387918736</v>
+        <v>0.0151473387918736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001545889007792084</v>
+        <v>0.01545889007792084</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00157679180887372</v>
+        <v>0.0157679180887372</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/92.xlsx
+++ b/BVSimulationFiles/92.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.00379</v>
+        <v>0.002483103448275862</v>
       </c>
       <c r="D1" t="n">
-        <v>0.00758</v>
+        <v>0.004966206896551723</v>
       </c>
       <c r="E1" t="n">
-        <v>0.01137</v>
+        <v>0.007449310344827586</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01516</v>
+        <v>0.009932413793103447</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01895</v>
+        <v>0.01241551724137931</v>
       </c>
       <c r="H1" t="n">
-        <v>0.02274</v>
+        <v>0.01489862068965517</v>
       </c>
       <c r="I1" t="n">
-        <v>0.02653</v>
+        <v>0.01738172413793103</v>
       </c>
       <c r="J1" t="n">
-        <v>0.03032</v>
+        <v>0.01986482758620689</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03411</v>
+        <v>0.02234793103448275</v>
       </c>
       <c r="L1" t="n">
-        <v>0.0379</v>
+        <v>0.02483103448275862</v>
       </c>
       <c r="M1" t="n">
-        <v>0.04169</v>
+        <v>0.02731413793103448</v>
       </c>
       <c r="N1" t="n">
-        <v>0.04548</v>
+        <v>0.02979724137931034</v>
       </c>
       <c r="O1" t="n">
-        <v>0.04926999999999999</v>
+        <v>0.0322803448275862</v>
       </c>
       <c r="P1" t="n">
-        <v>0.05306</v>
+        <v>0.03476344827586206</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.05685</v>
+        <v>0.03724655172413793</v>
       </c>
       <c r="R1" t="n">
-        <v>0.06064</v>
+        <v>0.03972965517241379</v>
       </c>
       <c r="S1" t="n">
-        <v>0.06443</v>
+        <v>0.04221275862068965</v>
       </c>
       <c r="T1" t="n">
-        <v>0.06822</v>
+        <v>0.04469586206896551</v>
       </c>
       <c r="U1" t="n">
+        <v>0.04717896551724137</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.04966206896551723</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.0521451724137931</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.05462827586206896</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.05711137931034482</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.05959448275862068</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.06207758620689655</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.06456068965517241</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.06704379310344827</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.06952689655172413</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.07200999999999999</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009450549450549449</v>
+        <v>0.05509529890070844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009807278567564887</v>
+        <v>0.05632220324117901</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01016122740008711</v>
+        <v>0.0575358686342205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01051241167994684</v>
+        <v>0.05873639484233222</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01086084706046746</v>
+        <v>0.05992388097073374</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01120654911683123</v>
+        <v>0.06109842547139908</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01154953334644374</v>
+        <v>0.06226012614706647</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01188981516929686</v>
+        <v>0.06340908015522513</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01222740992832996</v>
+        <v>0.06454538401207827</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01256233288978961</v>
+        <v>0.06566913359648299</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01289459924358759</v>
+        <v>0.06678042415386706</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01322422410365731</v>
+        <v>0.0678793503001224</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01355122250830875</v>
+        <v>0.06896600602547595</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01387560942058161</v>
+        <v>0.07004048469833782</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01419739972859707</v>
+        <v>0.07110287906912648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01451660824590783</v>
+        <v>0.0721532812740716</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01483324971184671</v>
+        <v>0.07319178283899491</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0151473387918736</v>
+        <v>0.07421847468306794</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01545889007792084</v>
+        <v>0.07523344712254866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0157679180887372</v>
+        <v>0.07623678987449542</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.07722859206045903</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.07820894221015368</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.0791779282651056</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.08013563758228061</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.08108215693769016</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.08201757252997602</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.08294196998397417</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.08385543435425719</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.0847580501286563</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08564990123176232</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009450549450549449</v>
+        <v>0.05509529890070844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009807278567564887</v>
+        <v>0.05632220324117901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01016122740008711</v>
+        <v>0.0575358686342205</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01051241167994684</v>
+        <v>0.05873639484233222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01086084706046746</v>
+        <v>0.05992388097073374</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01120654911683123</v>
+        <v>0.06109842547139908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01154953334644374</v>
+        <v>0.06226012614706647</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01188981516929686</v>
+        <v>0.06340908015522513</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01222740992832996</v>
+        <v>0.06454538401207827</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01256233288978961</v>
+        <v>0.06566913359648299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01289459924358759</v>
+        <v>0.06678042415386706</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01322422410365731</v>
+        <v>0.0678793503001224</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01355122250830875</v>
+        <v>0.06896600602547595</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01387560942058161</v>
+        <v>0.07004048469833782</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01419739972859707</v>
+        <v>0.07110287906912648</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01451660824590783</v>
+        <v>0.0721532812740716</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01483324971184671</v>
+        <v>0.07319178283899491</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0151473387918736</v>
+        <v>0.07421847468306794</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01545889007792084</v>
+        <v>0.07523344712254866</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0157679180887372</v>
+        <v>0.07623678987449542</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.07722859206045903</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.07820894221015368</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0791779282651056</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.08013563758228061</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.08108215693769016</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.08201757252997602</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.08294196998397417</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.08385543435425719</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.0847580501286563</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.08564990123176232</v>
       </c>
     </row>
   </sheetData>
